--- a/Order_Upload_Template.xlsx
+++ b/Order_Upload_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\01301F744\Desktop\Pfizer Project\Fiori Work\OrderUploadApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2852F06F-CD4D-4A6A-956E-1732AB7E0EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C67872-AFB7-4BCC-9A20-749D18BF2E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3332C325-B3C7-46D4-9D95-52398FA3E64F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>VBAK_AUART</t>
   </si>
@@ -204,16 +204,63 @@
   </si>
   <si>
     <t>FG100</t>
+  </si>
+  <si>
+    <t>Test Name1</t>
+  </si>
+  <si>
+    <t>Test name2</t>
+  </si>
+  <si>
+    <t>50 Goblin Street</t>
+  </si>
+  <si>
+    <t>Near SP School</t>
+  </si>
+  <si>
+    <t>OrdUpl@testmail.com</t>
+  </si>
+  <si>
+    <t>T2 Name1</t>
+  </si>
+  <si>
+    <t>T3 Name1</t>
+  </si>
+  <si>
+    <t>T2 name2</t>
+  </si>
+  <si>
+    <t>T3 name2</t>
+  </si>
+  <si>
+    <t>Near SP3 School</t>
+  </si>
+  <si>
+    <t>Near SP2 School</t>
+  </si>
+  <si>
+    <t>52 Goblin Street</t>
+  </si>
+  <si>
+    <t>53 Goblin Street</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -236,10 +283,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -247,8 +295,12 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -764,7 +816,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>54</v>
       </c>
@@ -794,14 +846,24 @@
       <c r="K3" s="1">
         <v>20250715</v>
       </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
+      <c r="S3" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="T3" s="1">
         <v>10</v>
       </c>
@@ -929,7 +991,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
@@ -959,14 +1021,24 @@
       <c r="K6" s="1">
         <v>20250715</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
+      <c r="S6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="T6" s="1">
         <v>10</v>
       </c>
@@ -984,7 +1056,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
@@ -1014,14 +1086,24 @@
       <c r="K7" s="1">
         <v>20260715</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
+      <c r="S7" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="T7" s="1">
         <v>10</v>
       </c>
@@ -1040,6 +1122,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="S3" r:id="rId1" xr:uid="{B6B7879D-27E5-4A1B-9D9B-1AC799945C79}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Order_Upload_Template.xlsx
+++ b/Order_Upload_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\01301F744\Desktop\Pfizer Project\Fiori Work\OrderUploadApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C67872-AFB7-4BCC-9A20-749D18BF2E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C52797F-CEBF-45B9-AC95-E4DC38474517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3332C325-B3C7-46D4-9D95-52398FA3E64F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>VBAK_AUART</t>
   </si>
@@ -200,9 +200,6 @@
     <t>DITL-UPS-SHP3</t>
   </si>
   <si>
-    <t>OR</t>
-  </si>
-  <si>
     <t>FG100</t>
   </si>
   <si>
@@ -243,12 +240,24 @@
   </si>
   <si>
     <t>53 Goblin Street</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>DITL-UPS-SHP4</t>
+  </si>
+  <si>
+    <t>DITL-UPS-SHP5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -287,7 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -298,6 +307,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -633,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3649C723-5A6D-4D15-9341-46BB655C5AC8}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
@@ -818,7 +831,7 @@
     </row>
     <row r="3" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1">
         <v>1010</v>
@@ -826,7 +839,7 @@
       <c r="C3" s="1">
         <v>10</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="4">
         <v>0</v>
       </c>
       <c r="E3" s="1"/>
@@ -847,28 +860,28 @@
         <v>20250715</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T3" s="1">
         <v>10</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V3" s="1">
         <v>1</v>
@@ -883,7 +896,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1">
         <v>1010</v>
@@ -891,7 +904,7 @@
       <c r="C4" s="1">
         <v>10</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="4">
         <v>0</v>
       </c>
       <c r="E4" s="1"/>
@@ -923,7 +936,7 @@
         <v>10</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V4" s="1">
         <v>1</v>
@@ -938,7 +951,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1">
         <v>1010</v>
@@ -946,7 +959,7 @@
       <c r="C5" s="1">
         <v>10</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="4">
         <v>0</v>
       </c>
       <c r="E5" s="1"/>
@@ -978,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V5" s="1">
         <v>1</v>
@@ -993,7 +1006,7 @@
     </row>
     <row r="6" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1">
         <v>1010</v>
@@ -1001,7 +1014,7 @@
       <c r="C6" s="1">
         <v>10</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="4">
         <v>0</v>
       </c>
       <c r="E6" s="1"/>
@@ -1013,7 +1026,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J6" s="1">
         <v>20250713</v>
@@ -1022,28 +1035,28 @@
         <v>20250715</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T6" s="1">
         <v>10</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V6" s="1">
         <v>1</v>
@@ -1058,7 +1071,7 @@
     </row>
     <row r="7" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1">
         <v>1010</v>
@@ -1066,7 +1079,7 @@
       <c r="C7" s="1">
         <v>10</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="4">
         <v>0</v>
       </c>
       <c r="E7" s="1"/>
@@ -1078,7 +1091,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="J7" s="1">
         <v>20260713</v>
@@ -1087,28 +1100,28 @@
         <v>20260715</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T7" s="1">
         <v>10</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V7" s="1">
         <v>1</v>
@@ -1120,6 +1133,105 @@
       <c r="Y7" s="1">
         <v>1010</v>
       </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D40" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
